--- a/output/nabos_04_01avg.xlsx
+++ b/output/nabos_04_01avg.xlsx
@@ -550,61 +550,61 @@
         <v>74.83178</v>
       </c>
       <c r="C2" t="n">
-        <v>170.80683</v>
+        <v>170.80684</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.2335</v>
+        <v>-1.2331</v>
       </c>
       <c r="F2" t="n">
         <v>-1.2336</v>
       </c>
       <c r="G2" t="n">
-        <v>22.046473</v>
+        <v>22.046559</v>
       </c>
       <c r="H2" t="n">
-        <v>22.039382</v>
+        <v>22.04239</v>
       </c>
       <c r="I2" t="n">
-        <v>26.9404</v>
+        <v>26.9403</v>
       </c>
       <c r="J2" t="n">
-        <v>26.9311</v>
+        <v>26.9353</v>
       </c>
       <c r="K2" t="n">
-        <v>374.441</v>
+        <v>374.438</v>
       </c>
       <c r="L2" t="n">
-        <v>365.63</v>
+        <v>365.62</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0496</v>
+        <v>-0.0397</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6166</v>
+        <v>4.6161</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1099</v>
+        <v>0.11</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1099</v>
+        <v>0.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0623</v>
+        <v>0.0627</v>
       </c>
       <c r="R2" t="n">
-        <v>0.023</v>
+        <v>0.0234</v>
       </c>
       <c r="S2" t="n">
-        <v>2663</v>
+        <v>2671</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8486</v>
+        <v>1.8543</v>
       </c>
       <c r="U2" t="n">
-        <v>67.57</v>
+        <v>67.52</v>
       </c>
       <c r="V2" t="n">
         <v>2.5886</v>
@@ -613,7 +613,7 @@
         <v>2.2482</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -648,34 +648,34 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2301</v>
+        <v>-1.2302</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.228</v>
+        <v>-1.2278</v>
       </c>
       <c r="G3" t="n">
-        <v>22.029132</v>
+        <v>22.027289</v>
       </c>
       <c r="H3" t="n">
-        <v>22.028164</v>
+        <v>22.026808</v>
       </c>
       <c r="I3" t="n">
-        <v>26.9137</v>
+        <v>26.9113</v>
       </c>
       <c r="J3" t="n">
-        <v>26.9105</v>
+        <v>26.9085</v>
       </c>
       <c r="K3" t="n">
-        <v>374.565</v>
+        <v>374.585</v>
       </c>
       <c r="L3" t="n">
-        <v>365.72</v>
+        <v>365.676</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0547</v>
+        <v>-0.0608</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6139</v>
+        <v>4.6144</v>
       </c>
       <c r="O3" t="n">
         <v>0.1083</v>
@@ -684,28 +684,28 @@
         <v>0.1083</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0646</v>
+        <v>0.0641</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0228</v>
+        <v>0.0226</v>
       </c>
       <c r="S3" t="n">
-        <v>2946</v>
+        <v>2960</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0449</v>
+        <v>2.0547</v>
       </c>
       <c r="U3" t="n">
-        <v>66.4</v>
+        <v>66.33</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5888</v>
+        <v>2.5889</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2484</v>
+        <v>2.2482</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4.948</v>
+        <v>4.947</v>
       </c>
       <c r="B4" t="n">
         <v>74.8318</v>
@@ -740,64 +740,64 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2339</v>
+        <v>-1.2323</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.232</v>
+        <v>-1.2313</v>
       </c>
       <c r="G4" t="n">
-        <v>22.027317</v>
+        <v>22.027261</v>
       </c>
       <c r="H4" t="n">
-        <v>22.025441</v>
+        <v>22.025108</v>
       </c>
       <c r="I4" t="n">
-        <v>26.9142</v>
+        <v>26.9128</v>
       </c>
       <c r="J4" t="n">
-        <v>26.91</v>
+        <v>26.909</v>
       </c>
       <c r="K4" t="n">
-        <v>374.774</v>
+        <v>374.761</v>
       </c>
       <c r="L4" t="n">
-        <v>365.799</v>
+        <v>365.87</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.049</v>
+        <v>-0.0458</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6165</v>
+        <v>4.6167</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1067</v>
+        <v>0.1064</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1067</v>
+        <v>0.1064</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0623</v>
+        <v>0.0621</v>
       </c>
       <c r="R4" t="n">
-        <v>0.023</v>
+        <v>0.0232</v>
       </c>
       <c r="S4" t="n">
-        <v>3059</v>
+        <v>3065</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1239</v>
+        <v>2.1279</v>
       </c>
       <c r="U4" t="n">
-        <v>45.17</v>
+        <v>40.5</v>
       </c>
       <c r="V4" t="n">
         <v>2.5895</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2483</v>
+        <v>2.2487</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.938</v>
+        <v>5.94</v>
       </c>
       <c r="B5" t="n">
         <v>74.8318</v>
@@ -832,34 +832,34 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2338</v>
+        <v>-1.2337</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2337</v>
+        <v>-1.2336</v>
       </c>
       <c r="G5" t="n">
-        <v>22.029347</v>
+        <v>22.029116</v>
       </c>
       <c r="H5" t="n">
-        <v>22.028456</v>
+        <v>22.028162</v>
       </c>
       <c r="I5" t="n">
-        <v>26.9163</v>
+        <v>26.916</v>
       </c>
       <c r="J5" t="n">
-        <v>26.915</v>
+        <v>26.9146</v>
       </c>
       <c r="K5" t="n">
-        <v>374.688</v>
+        <v>374.683</v>
       </c>
       <c r="L5" t="n">
-        <v>365.636</v>
+        <v>365.678</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0434</v>
+        <v>-0.0441</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6164</v>
+        <v>4.6162</v>
       </c>
       <c r="O5" t="n">
         <v>0.1054</v>
@@ -868,28 +868,28 @@
         <v>0.1054</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0624</v>
+        <v>0.0626</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0233</v>
+        <v>0.0232</v>
       </c>
       <c r="S5" t="n">
         <v>3125</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1691</v>
+        <v>2.1694</v>
       </c>
       <c r="U5" t="n">
-        <v>43.72</v>
+        <v>44.29</v>
       </c>
       <c r="V5" t="n">
         <v>2.5887</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2473</v>
+        <v>2.2475</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6.927</v>
+        <v>6.926</v>
       </c>
       <c r="B6" t="n">
         <v>74.8318</v>
@@ -924,64 +924,64 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.234</v>
+        <v>-1.2341</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2335</v>
+        <v>-1.2333</v>
       </c>
       <c r="G6" t="n">
-        <v>22.030306</v>
+        <v>22.030261</v>
       </c>
       <c r="H6" t="n">
-        <v>22.028854</v>
+        <v>22.028814</v>
       </c>
       <c r="I6" t="n">
         <v>26.9173</v>
       </c>
       <c r="J6" t="n">
-        <v>26.9148</v>
+        <v>26.9147</v>
       </c>
       <c r="K6" t="n">
-        <v>374.6</v>
+        <v>374.575</v>
       </c>
       <c r="L6" t="n">
-        <v>365.662</v>
+        <v>365.734</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0435</v>
+        <v>-0.0396</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6159</v>
+        <v>4.616</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1065</v>
+        <v>0.107</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1065</v>
+        <v>0.107</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0628</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0233</v>
+        <v>0.0234</v>
       </c>
       <c r="S6" t="n">
-        <v>3218</v>
+        <v>3223</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2338</v>
+        <v>2.2378</v>
       </c>
       <c r="U6" t="n">
-        <v>50.55</v>
+        <v>51</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5879</v>
+        <v>2.5878</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2472</v>
+        <v>2.2476</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>-1.2333</v>
       </c>
       <c r="G7" t="n">
-        <v>22.030221</v>
+        <v>22.030194</v>
       </c>
       <c r="H7" t="n">
-        <v>22.029436</v>
+        <v>22.029415</v>
       </c>
       <c r="I7" t="n">
         <v>26.9164</v>
@@ -1034,16 +1034,16 @@
         <v>26.9149</v>
       </c>
       <c r="K7" t="n">
-        <v>374.441</v>
+        <v>374.447</v>
       </c>
       <c r="L7" t="n">
-        <v>365.777</v>
+        <v>365.771</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0146</v>
+        <v>-0.0124</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6149</v>
+        <v>4.6148</v>
       </c>
       <c r="O7" t="n">
         <v>0.1045</v>
@@ -1052,28 +1052,28 @@
         <v>0.1045</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0637</v>
+        <v>0.0638</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
       <c r="S7" t="n">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2868</v>
+        <v>2.2872</v>
       </c>
       <c r="U7" t="n">
-        <v>48.76</v>
+        <v>48.65</v>
       </c>
       <c r="V7" t="n">
         <v>2.5868</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2476</v>
+        <v>2.2475</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1111,61 +1111,61 @@
         <v>-1.2342</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2337</v>
+        <v>-1.2335</v>
       </c>
       <c r="G8" t="n">
-        <v>22.032823</v>
+        <v>22.03261</v>
       </c>
       <c r="H8" t="n">
-        <v>22.031342</v>
+        <v>22.031046</v>
       </c>
       <c r="I8" t="n">
-        <v>26.9198</v>
+        <v>26.9195</v>
       </c>
       <c r="J8" t="n">
-        <v>26.9173</v>
+        <v>26.9168</v>
       </c>
       <c r="K8" t="n">
-        <v>379.663</v>
+        <v>378.475</v>
       </c>
       <c r="L8" t="n">
-        <v>365.698</v>
+        <v>365.734</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.008</v>
+        <v>-0.0101</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6178</v>
+        <v>4.6179</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1053</v>
+        <v>0.1052</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1053</v>
+        <v>0.1052</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0612</v>
+        <v>0.0611</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0247</v>
+        <v>0.0246</v>
       </c>
       <c r="S8" t="n">
-        <v>3374</v>
+        <v>3377</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3426</v>
+        <v>2.3447</v>
       </c>
       <c r="U8" t="n">
-        <v>46.61</v>
+        <v>44.56</v>
       </c>
       <c r="V8" t="n">
-        <v>2.6157</v>
+        <v>2.6091</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2469</v>
+        <v>2.2471</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9.896</v>
+        <v>9.895</v>
       </c>
       <c r="B9" t="n">
         <v>74.83182</v>
@@ -1206,34 +1206,34 @@
         <v>-1.2356</v>
       </c>
       <c r="G9" t="n">
-        <v>22.025888</v>
+        <v>22.024794</v>
       </c>
       <c r="H9" t="n">
-        <v>22.027397</v>
+        <v>22.025912</v>
       </c>
       <c r="I9" t="n">
-        <v>26.9119</v>
+        <v>26.9105</v>
       </c>
       <c r="J9" t="n">
-        <v>26.9132</v>
+        <v>26.9114</v>
       </c>
       <c r="K9" t="n">
-        <v>376.269</v>
+        <v>376.221</v>
       </c>
       <c r="L9" t="n">
-        <v>365.781</v>
+        <v>365.798</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.011</v>
+        <v>-0.0115</v>
       </c>
       <c r="N9" t="n">
         <v>4.6184</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1107</v>
+        <v>0.1105</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1107</v>
+        <v>0.1105</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0607</v>
@@ -1245,19 +1245,19 @@
         <v>3451</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3956</v>
+        <v>2.3961</v>
       </c>
       <c r="U9" t="n">
-        <v>58.95</v>
+        <v>58.89</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5962</v>
+        <v>2.5959</v>
       </c>
       <c r="W9" t="n">
         <v>2.247</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10.885</v>
+        <v>10.887</v>
       </c>
       <c r="B10" t="n">
         <v>74.83182</v>
@@ -1292,64 +1292,64 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2387</v>
+        <v>-1.2386</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2382</v>
+        <v>-1.2381</v>
       </c>
       <c r="G10" t="n">
-        <v>22.014342</v>
+        <v>22.014726</v>
       </c>
       <c r="H10" t="n">
-        <v>22.013226</v>
+        <v>22.013638</v>
       </c>
       <c r="I10" t="n">
-        <v>26.8981</v>
+        <v>26.8987</v>
       </c>
       <c r="J10" t="n">
-        <v>26.8961</v>
+        <v>26.8968</v>
       </c>
       <c r="K10" t="n">
-        <v>375.18</v>
+        <v>375.205</v>
       </c>
       <c r="L10" t="n">
-        <v>365.859</v>
+        <v>365.848</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0262</v>
+        <v>-0.025</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6144</v>
+        <v>4.6151</v>
       </c>
       <c r="O10" t="n">
-        <v>0.109</v>
+        <v>0.1093</v>
       </c>
       <c r="P10" t="n">
-        <v>0.109</v>
+        <v>0.1093</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0641</v>
+        <v>0.0635</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="S10" t="n">
-        <v>3497</v>
+        <v>3499</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4275</v>
+        <v>2.4293</v>
       </c>
       <c r="U10" t="n">
-        <v>59.39</v>
+        <v>59.26</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5895</v>
+        <v>2.5896</v>
       </c>
       <c r="W10" t="n">
         <v>2.2467</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1384,31 +1384,31 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2403</v>
+        <v>-1.2404</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2409</v>
+        <v>-1.2408</v>
       </c>
       <c r="G11" t="n">
-        <v>22.016987</v>
+        <v>22.017057</v>
       </c>
       <c r="H11" t="n">
-        <v>22.017</v>
+        <v>22.016869</v>
       </c>
       <c r="I11" t="n">
-        <v>26.9026</v>
+        <v>26.9029</v>
       </c>
       <c r="J11" t="n">
-        <v>26.9031</v>
+        <v>26.903</v>
       </c>
       <c r="K11" t="n">
-        <v>374.965</v>
+        <v>374.942</v>
       </c>
       <c r="L11" t="n">
-        <v>365.846</v>
+        <v>365.829</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0039</v>
+        <v>-0.0035</v>
       </c>
       <c r="N11" t="n">
         <v>4.618</v>
@@ -1426,22 +1426,22 @@
         <v>0.0248</v>
       </c>
       <c r="S11" t="n">
-        <v>3564</v>
+        <v>3566</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4745</v>
+        <v>2.4758</v>
       </c>
       <c r="U11" t="n">
-        <v>58.36</v>
+        <v>58.34</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5879</v>
+        <v>2.5878</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2464</v>
+        <v>2.2463</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12.865</v>
+        <v>12.864</v>
       </c>
       <c r="B12" t="n">
         <v>74.83184</v>
@@ -1482,28 +1482,28 @@
         <v>-1.249</v>
       </c>
       <c r="G12" t="n">
-        <v>22.036925</v>
+        <v>22.03693</v>
       </c>
       <c r="H12" t="n">
-        <v>22.028582</v>
+        <v>22.028072</v>
       </c>
       <c r="I12" t="n">
-        <v>26.9366</v>
+        <v>26.9371</v>
       </c>
       <c r="J12" t="n">
-        <v>26.9254</v>
+        <v>26.9251</v>
       </c>
       <c r="K12" t="n">
-        <v>374.766</v>
+        <v>374.779</v>
       </c>
       <c r="L12" t="n">
-        <v>366.076</v>
+        <v>366.028</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6175</v>
+        <v>4.6174</v>
       </c>
       <c r="O12" t="n">
         <v>0.1094</v>
@@ -1512,28 +1512,28 @@
         <v>0.1094</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0614</v>
+        <v>0.0615</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0248</v>
+        <v>0.0249</v>
       </c>
       <c r="S12" t="n">
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5193</v>
+        <v>2.5203</v>
       </c>
       <c r="U12" t="n">
-        <v>57.36</v>
+        <v>57.34</v>
       </c>
       <c r="V12" t="n">
         <v>2.5866</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2471</v>
+        <v>2.2469</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1568,64 +1568,64 @@
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2438</v>
+        <v>-1.2397</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2431</v>
+        <v>-1.2405</v>
       </c>
       <c r="G13" t="n">
-        <v>22.078207</v>
+        <v>22.11524</v>
       </c>
       <c r="H13" t="n">
-        <v>22.068703</v>
+        <v>22.096752</v>
       </c>
       <c r="I13" t="n">
-        <v>26.9865</v>
+        <v>27.0321</v>
       </c>
       <c r="J13" t="n">
-        <v>26.9731</v>
+        <v>27.0082</v>
       </c>
       <c r="K13" t="n">
-        <v>374.576</v>
+        <v>374.393</v>
       </c>
       <c r="L13" t="n">
-        <v>365.706</v>
+        <v>365.518</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0055</v>
+        <v>0.0078</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6163</v>
+        <v>4.6159</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1085</v>
+        <v>0.1084</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1085</v>
+        <v>0.1084</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0626</v>
+        <v>0.0628</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0252</v>
+        <v>0.0253</v>
       </c>
       <c r="S13" t="n">
-        <v>3682</v>
+        <v>3683</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5565</v>
+        <v>2.5573</v>
       </c>
       <c r="U13" t="n">
-        <v>56.09</v>
+        <v>55.93</v>
       </c>
       <c r="V13" t="n">
         <v>2.5864</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2461</v>
+        <v>2.2458</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14.844</v>
+        <v>14.845</v>
       </c>
       <c r="B14" t="n">
         <v>74.83184</v>
@@ -1660,64 +1660,64 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1261</v>
+        <v>-1.1313</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1333</v>
+        <v>-1.1362</v>
       </c>
       <c r="G14" t="n">
-        <v>23.089538</v>
+        <v>23.043036</v>
       </c>
       <c r="H14" t="n">
-        <v>23.033066</v>
+        <v>23.006546</v>
       </c>
       <c r="I14" t="n">
-        <v>28.2299</v>
+        <v>28.1692</v>
       </c>
       <c r="J14" t="n">
-        <v>28.1611</v>
+        <v>28.1252</v>
       </c>
       <c r="K14" t="n">
-        <v>369.834</v>
+        <v>370.093</v>
       </c>
       <c r="L14" t="n">
-        <v>360.824</v>
+        <v>361.037</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0905</v>
+        <v>0.0942</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6159</v>
+        <v>4.6163</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1055</v>
+        <v>0.1056</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1055</v>
+        <v>0.1056</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0628</v>
+        <v>0.0624</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0286</v>
+        <v>0.0288</v>
       </c>
       <c r="S14" t="n">
-        <v>3735</v>
+        <v>3738</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5931</v>
+        <v>2.595</v>
       </c>
       <c r="U14" t="n">
-        <v>34.84</v>
+        <v>34.44</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5875</v>
+        <v>2.5876</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2446</v>
+        <v>2.245</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15.833</v>
+        <v>15.83</v>
       </c>
       <c r="B15" t="n">
         <v>74.83184</v>
@@ -1752,64 +1752,64 @@
         <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1107</v>
+        <v>-1.1095</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1099</v>
+        <v>-1.1085</v>
       </c>
       <c r="G15" t="n">
-        <v>23.224182</v>
+        <v>23.229843</v>
       </c>
       <c r="H15" t="n">
-        <v>23.235957</v>
+        <v>23.247163</v>
       </c>
       <c r="I15" t="n">
-        <v>28.395</v>
+        <v>28.3988</v>
       </c>
       <c r="J15" t="n">
-        <v>28.4101</v>
+        <v>28.421</v>
       </c>
       <c r="K15" t="n">
-        <v>369.202</v>
+        <v>369.189</v>
       </c>
       <c r="L15" t="n">
-        <v>360.136</v>
+        <v>360.138</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1338</v>
+        <v>0.1379</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6124</v>
+        <v>4.6132</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1098</v>
+        <v>0.1097</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1098</v>
+        <v>0.1097</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0659</v>
+        <v>0.0652</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0303</v>
+        <v>0.0305</v>
       </c>
       <c r="S15" t="n">
-        <v>3805</v>
+        <v>3807</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6417</v>
+        <v>2.6432</v>
       </c>
       <c r="U15" t="n">
-        <v>47.32</v>
+        <v>46.86</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5873</v>
+        <v>2.5874</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2457</v>
+        <v>2.2459</v>
       </c>
       <c r="X15" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1844,64 +1844,64 @@
         <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0874</v>
+        <v>-1.0877</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.088</v>
+        <v>-1.0883</v>
       </c>
       <c r="G16" t="n">
-        <v>23.503051</v>
+        <v>23.505019</v>
       </c>
       <c r="H16" t="n">
-        <v>23.497033</v>
+        <v>23.497237</v>
       </c>
       <c r="I16" t="n">
-        <v>28.7458</v>
+        <v>28.7459</v>
       </c>
       <c r="J16" t="n">
-        <v>28.7382</v>
+        <v>28.736</v>
       </c>
       <c r="K16" t="n">
-        <v>367.94</v>
+        <v>367.922</v>
       </c>
       <c r="L16" t="n">
-        <v>359.29</v>
+        <v>359.291</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1335</v>
+        <v>0.135</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5877</v>
+        <v>4.5897</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1106</v>
+        <v>0.1107</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1106</v>
+        <v>0.1107</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0874</v>
+        <v>0.0857</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0303</v>
+        <v>0.0304</v>
       </c>
       <c r="S16" t="n">
-        <v>3851</v>
+        <v>3852</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6734</v>
+        <v>2.674</v>
       </c>
       <c r="U16" t="n">
-        <v>53.11</v>
+        <v>53.13</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5871</v>
+        <v>2.587</v>
       </c>
       <c r="W16" t="n">
         <v>2.247</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17.812</v>
+        <v>17.814</v>
       </c>
       <c r="B17" t="n">
         <v>74.83184</v>
@@ -1936,34 +1936,34 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0902</v>
+        <v>-1.0901</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0886</v>
+        <v>-1.0885</v>
       </c>
       <c r="G17" t="n">
-        <v>23.495103</v>
+        <v>23.49885</v>
       </c>
       <c r="H17" t="n">
-        <v>23.495276</v>
+        <v>23.498018</v>
       </c>
       <c r="I17" t="n">
-        <v>28.7372</v>
+        <v>28.7401</v>
       </c>
       <c r="J17" t="n">
-        <v>28.7359</v>
+        <v>28.7374</v>
       </c>
       <c r="K17" t="n">
-        <v>368.107</v>
+        <v>368.128</v>
       </c>
       <c r="L17" t="n">
-        <v>359.887</v>
+        <v>359.853</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1424</v>
+        <v>0.1441</v>
       </c>
       <c r="N17" t="n">
-        <v>4.617</v>
+        <v>4.6158</v>
       </c>
       <c r="O17" t="n">
         <v>0.1101</v>
@@ -1972,28 +1972,28 @@
         <v>0.1101</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0618</v>
+        <v>0.0629</v>
       </c>
       <c r="R17" t="n">
         <v>0.0307</v>
       </c>
       <c r="S17" t="n">
-        <v>3893</v>
+        <v>3895</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7029</v>
+        <v>2.7041</v>
       </c>
       <c r="U17" t="n">
-        <v>48.49</v>
+        <v>49.36</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5875</v>
+        <v>2.5876</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2496</v>
+        <v>2.2494</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18.802</v>
+        <v>18.801</v>
       </c>
       <c r="B18" t="n">
         <v>74.83186</v>
@@ -2028,64 +2028,64 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0916</v>
+        <v>-1.0917</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0917</v>
+        <v>-1.092</v>
       </c>
       <c r="G18" t="n">
-        <v>23.48045</v>
+        <v>23.480338</v>
       </c>
       <c r="H18" t="n">
-        <v>23.475431</v>
+        <v>23.474915</v>
       </c>
       <c r="I18" t="n">
-        <v>28.7184</v>
+        <v>28.7169</v>
       </c>
       <c r="J18" t="n">
-        <v>28.7118</v>
+        <v>28.71</v>
       </c>
       <c r="K18" t="n">
-        <v>368.543</v>
+        <v>368.519</v>
       </c>
       <c r="L18" t="n">
-        <v>359.934</v>
+        <v>359.91</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1675</v>
+        <v>0.1676</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6165</v>
+        <v>4.6167</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1113</v>
+        <v>0.1115</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1113</v>
+        <v>0.1115</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0623</v>
+        <v>0.0621</v>
       </c>
       <c r="R18" t="n">
         <v>0.0317</v>
       </c>
       <c r="S18" t="n">
-        <v>3953</v>
+        <v>3955</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7443</v>
+        <v>2.7459</v>
       </c>
       <c r="U18" t="n">
-        <v>51.13</v>
+        <v>51.19</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5893</v>
+        <v>2.5891</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2491</v>
+        <v>2.249</v>
       </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19.791</v>
+        <v>19.789</v>
       </c>
       <c r="B19" t="n">
         <v>74.83186</v>
@@ -2120,43 +2120,43 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0785</v>
+        <v>-1.0787</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.082</v>
+        <v>-1.0807</v>
       </c>
       <c r="G19" t="n">
-        <v>23.525492</v>
+        <v>23.524925</v>
       </c>
       <c r="H19" t="n">
-        <v>23.510799</v>
+        <v>23.513588</v>
       </c>
       <c r="I19" t="n">
-        <v>28.7656</v>
+        <v>28.7636</v>
       </c>
       <c r="J19" t="n">
-        <v>28.7493</v>
+        <v>28.7504</v>
       </c>
       <c r="K19" t="n">
-        <v>368.546</v>
+        <v>368.567</v>
       </c>
       <c r="L19" t="n">
-        <v>359.756</v>
+        <v>359.78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1655</v>
+        <v>0.1651</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6174</v>
+        <v>4.6177</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1085</v>
+        <v>0.1086</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1085</v>
+        <v>0.1086</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0615</v>
+        <v>0.0612</v>
       </c>
       <c r="R19" t="n">
         <v>0.0316</v>
@@ -2165,19 +2165,19 @@
         <v>4005</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7803</v>
+        <v>2.7804</v>
       </c>
       <c r="U19" t="n">
-        <v>50.02</v>
+        <v>50.01</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5907</v>
+        <v>2.5908</v>
       </c>
       <c r="W19" t="n">
-        <v>2.249</v>
+        <v>2.2492</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20.781</v>
+        <v>20.784</v>
       </c>
       <c r="B20" t="n">
         <v>74.83186</v>
@@ -2212,64 +2212,64 @@
         <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0526</v>
+        <v>-1.0534</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.053</v>
+        <v>-1.0543</v>
       </c>
       <c r="G20" t="n">
-        <v>23.600165</v>
+        <v>23.603014</v>
       </c>
       <c r="H20" t="n">
-        <v>23.602693</v>
+        <v>23.604167</v>
       </c>
       <c r="I20" t="n">
-        <v>28.8402</v>
+        <v>28.8429</v>
       </c>
       <c r="J20" t="n">
-        <v>28.844</v>
+        <v>28.8453</v>
       </c>
       <c r="K20" t="n">
-        <v>368.238</v>
+        <v>368.237</v>
       </c>
       <c r="L20" t="n">
-        <v>359.472</v>
+        <v>359.528</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1557</v>
+        <v>0.1528</v>
       </c>
       <c r="N20" t="n">
         <v>4.6196</v>
       </c>
       <c r="O20" t="n">
-        <v>0.109</v>
+        <v>0.1091</v>
       </c>
       <c r="P20" t="n">
-        <v>0.109</v>
+        <v>0.1091</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0596</v>
+        <v>0.0597</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0312</v>
+        <v>0.0311</v>
       </c>
       <c r="S20" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8076</v>
+        <v>2.8085</v>
       </c>
       <c r="U20" t="n">
-        <v>49</v>
+        <v>48.98</v>
       </c>
       <c r="V20" t="n">
         <v>2.5915</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2502</v>
+        <v>2.2505</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21.77</v>
+        <v>21.769</v>
       </c>
       <c r="B21" t="n">
         <v>74.83186</v>
@@ -2304,64 +2304,64 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0845</v>
+        <v>-1.0855</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0861</v>
+        <v>-1.0872</v>
       </c>
       <c r="G21" t="n">
-        <v>23.614768</v>
+        <v>23.614582</v>
       </c>
       <c r="H21" t="n">
-        <v>23.613287</v>
+        <v>23.613429</v>
       </c>
       <c r="I21" t="n">
-        <v>28.89</v>
+        <v>28.8902</v>
       </c>
       <c r="J21" t="n">
-        <v>28.8895</v>
+        <v>28.8904</v>
       </c>
       <c r="K21" t="n">
-        <v>368.629</v>
+        <v>368.656</v>
       </c>
       <c r="L21" t="n">
-        <v>359.998</v>
+        <v>360.043</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1776</v>
+        <v>0.1775</v>
       </c>
       <c r="N21" t="n">
-        <v>4.617</v>
+        <v>4.6175</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1109</v>
+        <v>0.1107</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1109</v>
+        <v>0.1107</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0619</v>
+        <v>0.0615</v>
       </c>
       <c r="R21" t="n">
         <v>0.0321</v>
       </c>
       <c r="S21" t="n">
-        <v>4104</v>
+        <v>4106</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8491</v>
+        <v>2.8508</v>
       </c>
       <c r="U21" t="n">
-        <v>47.99</v>
+        <v>47.96</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5922</v>
+        <v>2.5923</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2514</v>
+        <v>2.2516</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22.76</v>
+        <v>22.758</v>
       </c>
       <c r="B22" t="n">
         <v>74.83186</v>
@@ -2396,64 +2396,64 @@
         <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1449</v>
+        <v>-1.1467</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1437</v>
+        <v>-1.1453</v>
       </c>
       <c r="G22" t="n">
-        <v>23.625053</v>
+        <v>23.623089</v>
       </c>
       <c r="H22" t="n">
-        <v>23.622221</v>
+        <v>23.620427</v>
       </c>
       <c r="I22" t="n">
-        <v>28.9615</v>
+        <v>28.9622</v>
       </c>
       <c r="J22" t="n">
-        <v>28.9565</v>
+        <v>28.9572</v>
       </c>
       <c r="K22" t="n">
-        <v>368.728</v>
+        <v>368.723</v>
       </c>
       <c r="L22" t="n">
-        <v>360.456</v>
+        <v>360.462</v>
       </c>
       <c r="M22" t="n">
-        <v>0.191</v>
+        <v>0.1901</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6205</v>
+        <v>4.6206</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1103</v>
+        <v>0.1102</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1103</v>
+        <v>0.1102</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0589</v>
+        <v>0.0588</v>
       </c>
       <c r="R22" t="n">
         <v>0.0326</v>
       </c>
       <c r="S22" t="n">
-        <v>4159</v>
+        <v>4161</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8878</v>
+        <v>2.8888</v>
       </c>
       <c r="U22" t="n">
-        <v>46.96</v>
+        <v>46.94</v>
       </c>
       <c r="V22" t="n">
-        <v>2.5899</v>
+        <v>2.5897</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2513</v>
+        <v>2.2512</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23.749</v>
+        <v>23.751</v>
       </c>
       <c r="B23" t="n">
         <v>74.83186</v>
@@ -2488,64 +2488,64 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1624</v>
+        <v>-1.1625</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.162</v>
+        <v>-1.1621</v>
       </c>
       <c r="G23" t="n">
-        <v>23.65969</v>
+        <v>23.658663</v>
       </c>
       <c r="H23" t="n">
-        <v>23.658652</v>
+        <v>23.657693</v>
       </c>
       <c r="I23" t="n">
-        <v>29.0244</v>
+        <v>29.025</v>
       </c>
       <c r="J23" t="n">
-        <v>29.0227</v>
+        <v>29.0232</v>
       </c>
       <c r="K23" t="n">
-        <v>368.119</v>
+        <v>368.11</v>
       </c>
       <c r="L23" t="n">
-        <v>360.256</v>
+        <v>360.223</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2427</v>
+        <v>0.2452</v>
       </c>
       <c r="N23" t="n">
         <v>4.6214</v>
       </c>
       <c r="O23" t="n">
-        <v>0.111</v>
+        <v>0.1111</v>
       </c>
       <c r="P23" t="n">
-        <v>0.111</v>
+        <v>0.1111</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0581</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0347</v>
+        <v>0.0348</v>
       </c>
       <c r="S23" t="n">
-        <v>4199</v>
+        <v>4201</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9155</v>
+        <v>2.9164</v>
       </c>
       <c r="U23" t="n">
-        <v>45.91</v>
+        <v>45.87</v>
       </c>
       <c r="V23" t="n">
         <v>2.586</v>
       </c>
       <c r="W23" t="n">
-        <v>2.25</v>
+        <v>2.2499</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24.739</v>
+        <v>24.74</v>
       </c>
       <c r="B24" t="n">
         <v>74.83187</v>
@@ -2580,34 +2580,34 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.167</v>
+        <v>-1.1673</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1665</v>
+        <v>-1.1668</v>
       </c>
       <c r="G24" t="n">
-        <v>23.689361</v>
+        <v>23.688844</v>
       </c>
       <c r="H24" t="n">
-        <v>23.688185</v>
+        <v>23.687726</v>
       </c>
       <c r="I24" t="n">
-        <v>29.0682</v>
+        <v>29.0693</v>
       </c>
       <c r="J24" t="n">
-        <v>29.0662</v>
+        <v>29.0673</v>
       </c>
       <c r="K24" t="n">
-        <v>367.063</v>
+        <v>367.019</v>
       </c>
       <c r="L24" t="n">
-        <v>359.626</v>
+        <v>359.644</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2869</v>
+        <v>0.2857</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6182</v>
+        <v>4.6175</v>
       </c>
       <c r="O24" t="n">
         <v>0.111</v>
@@ -2616,28 +2616,28 @@
         <v>0.111</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0609</v>
+        <v>0.0615</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
       <c r="S24" t="n">
-        <v>4250</v>
+        <v>4252</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9508</v>
+        <v>2.9518</v>
       </c>
       <c r="U24" t="n">
-        <v>44.82</v>
+        <v>44.8</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5802</v>
+        <v>2.5799</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2471</v>
+        <v>2.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25.728</v>
+        <v>25.727</v>
       </c>
       <c r="B25" t="n">
         <v>74.83188</v>
@@ -2672,64 +2672,64 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1316</v>
+        <v>-1.1314</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.128</v>
+        <v>-1.1274</v>
       </c>
       <c r="G25" t="n">
-        <v>23.754857</v>
+        <v>23.755994</v>
       </c>
       <c r="H25" t="n">
-        <v>23.756261</v>
+        <v>23.757915</v>
       </c>
       <c r="I25" t="n">
-        <v>29.1213</v>
+        <v>29.1225</v>
       </c>
       <c r="J25" t="n">
-        <v>29.1197</v>
+        <v>29.1211</v>
       </c>
       <c r="K25" t="n">
-        <v>365.399</v>
+        <v>365.383</v>
       </c>
       <c r="L25" t="n">
-        <v>357.662</v>
+        <v>357.635</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3634</v>
+        <v>0.3596</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6203</v>
+        <v>4.6202</v>
       </c>
       <c r="O25" t="n">
-        <v>0.111</v>
+        <v>0.1108</v>
       </c>
       <c r="P25" t="n">
-        <v>0.111</v>
+        <v>0.1108</v>
       </c>
       <c r="Q25" t="n">
         <v>0.0591</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0396</v>
+        <v>0.0394</v>
       </c>
       <c r="S25" t="n">
-        <v>4309</v>
+        <v>4310</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9916</v>
+        <v>2.9926</v>
       </c>
       <c r="U25" t="n">
-        <v>43.85</v>
+        <v>43.82</v>
       </c>
       <c r="V25" t="n">
         <v>2.5735</v>
       </c>
       <c r="W25" t="n">
-        <v>2.2402</v>
+        <v>2.2401</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2764,64 +2764,64 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.167</v>
+        <v>-1.1726</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1654</v>
+        <v>-1.171</v>
       </c>
       <c r="G26" t="n">
-        <v>23.771831</v>
+        <v>23.76732</v>
       </c>
       <c r="H26" t="n">
-        <v>23.771737</v>
+        <v>23.767214</v>
       </c>
       <c r="I26" t="n">
-        <v>29.178</v>
+        <v>29.1787</v>
       </c>
       <c r="J26" t="n">
-        <v>29.1764</v>
+        <v>29.1771</v>
       </c>
       <c r="K26" t="n">
-        <v>365.179</v>
+        <v>365.193</v>
       </c>
       <c r="L26" t="n">
-        <v>357.472</v>
+        <v>357.559</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4094</v>
+        <v>0.4084</v>
       </c>
       <c r="N26" t="n">
         <v>4.618</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1095</v>
+        <v>0.1094</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1095</v>
+        <v>0.1094</v>
       </c>
       <c r="Q26" t="n">
         <v>0.061</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0414</v>
+        <v>0.0413</v>
       </c>
       <c r="S26" t="n">
-        <v>4359</v>
+        <v>4360</v>
       </c>
       <c r="T26" t="n">
-        <v>3.0264</v>
+        <v>3.0274</v>
       </c>
       <c r="U26" t="n">
-        <v>42.83</v>
+        <v>42.8</v>
       </c>
       <c r="V26" t="n">
-        <v>2.5707</v>
+        <v>2.5704</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2379</v>
+        <v>2.238</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27.708</v>
+        <v>27.706</v>
       </c>
       <c r="B27" t="n">
         <v>74.83188</v>
@@ -2856,31 +2856,31 @@
         <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.2187</v>
+        <v>-1.2184</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2185</v>
+        <v>-1.2182</v>
       </c>
       <c r="G27" t="n">
-        <v>23.759011</v>
+        <v>23.757932</v>
       </c>
       <c r="H27" t="n">
-        <v>23.757197</v>
+        <v>23.75606</v>
       </c>
       <c r="I27" t="n">
-        <v>29.2107</v>
+        <v>29.2113</v>
       </c>
       <c r="J27" t="n">
-        <v>29.208</v>
+        <v>29.2086</v>
       </c>
       <c r="K27" t="n">
-        <v>364.739</v>
+        <v>364.682</v>
       </c>
       <c r="L27" t="n">
-        <v>357.199</v>
+        <v>357.187</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4528</v>
+        <v>0.4511</v>
       </c>
       <c r="N27" t="n">
         <v>4.6175</v>
@@ -2898,22 +2898,22 @@
         <v>0.0431</v>
       </c>
       <c r="S27" t="n">
-        <v>4409</v>
+        <v>4410</v>
       </c>
       <c r="T27" t="n">
-        <v>3.0608</v>
+        <v>3.0616</v>
       </c>
       <c r="U27" t="n">
-        <v>41.72</v>
+        <v>41.7</v>
       </c>
       <c r="V27" t="n">
-        <v>2.5652</v>
+        <v>2.5649</v>
       </c>
       <c r="W27" t="n">
-        <v>2.234</v>
+        <v>2.2339</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28.697</v>
+        <v>28.698</v>
       </c>
       <c r="B28" t="n">
         <v>74.83188</v>
@@ -2948,55 +2948,55 @@
         <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2123</v>
+        <v>-1.2127</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.212</v>
+        <v>-1.2124</v>
       </c>
       <c r="G28" t="n">
-        <v>23.781996</v>
+        <v>23.781192</v>
       </c>
       <c r="H28" t="n">
-        <v>23.780446</v>
+        <v>23.779693</v>
       </c>
       <c r="I28" t="n">
-        <v>29.2349</v>
+        <v>29.2357</v>
       </c>
       <c r="J28" t="n">
-        <v>29.2325</v>
+        <v>29.2334</v>
       </c>
       <c r="K28" t="n">
-        <v>364.705</v>
+        <v>364.707</v>
       </c>
       <c r="L28" t="n">
-        <v>356.87</v>
+        <v>356.868</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4649</v>
+        <v>0.4697</v>
       </c>
       <c r="N28" t="n">
-        <v>4.616</v>
+        <v>4.6159</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1094</v>
+        <v>0.1093</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1094</v>
+        <v>0.1093</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0627</v>
+        <v>0.0628</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0436</v>
+        <v>0.0438</v>
       </c>
       <c r="S28" t="n">
-        <v>4454</v>
+        <v>4455</v>
       </c>
       <c r="T28" t="n">
-        <v>3.0926</v>
+        <v>3.0934</v>
       </c>
       <c r="U28" t="n">
-        <v>40.08</v>
+        <v>39.69</v>
       </c>
       <c r="V28" t="n">
         <v>2.5655</v>
@@ -3005,7 +3005,7 @@
         <v>2.2328</v>
       </c>
       <c r="X28" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3040,64 +3040,64 @@
         <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.2175</v>
+        <v>-1.2178</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.2171</v>
+        <v>-1.2173</v>
       </c>
       <c r="G29" t="n">
-        <v>23.799744</v>
+        <v>23.799268</v>
       </c>
       <c r="H29" t="n">
-        <v>23.798978</v>
+        <v>23.798517</v>
       </c>
       <c r="I29" t="n">
-        <v>29.2633</v>
+        <v>29.2642</v>
       </c>
       <c r="J29" t="n">
-        <v>29.2619</v>
+        <v>29.2628</v>
       </c>
       <c r="K29" t="n">
-        <v>363.925</v>
+        <v>363.846</v>
       </c>
       <c r="L29" t="n">
-        <v>356.523</v>
+        <v>356.388</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5193</v>
+        <v>0.5211</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6126</v>
+        <v>4.6123</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1088</v>
+        <v>0.109</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1088</v>
+        <v>0.109</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0657</v>
+        <v>0.066</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0458</v>
+        <v>0.0459</v>
       </c>
       <c r="S29" t="n">
-        <v>4510</v>
+        <v>4512</v>
       </c>
       <c r="T29" t="n">
-        <v>3.131</v>
+        <v>3.1328</v>
       </c>
       <c r="U29" t="n">
-        <v>30.38</v>
+        <v>30.7</v>
       </c>
       <c r="V29" t="n">
-        <v>2.561</v>
+        <v>2.5605</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2311</v>
+        <v>2.2304</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30.676</v>
+        <v>30.675</v>
       </c>
       <c r="B30" t="n">
         <v>74.8319</v>
@@ -3135,61 +3135,61 @@
         <v>-1.2444</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.2438</v>
+        <v>-1.2439</v>
       </c>
       <c r="G30" t="n">
-        <v>23.801649</v>
+        <v>23.800691</v>
       </c>
       <c r="H30" t="n">
-        <v>23.801245</v>
+        <v>23.800232</v>
       </c>
       <c r="I30" t="n">
-        <v>29.2917</v>
+        <v>29.2922</v>
       </c>
       <c r="J30" t="n">
-        <v>29.2905</v>
+        <v>29.2911</v>
       </c>
       <c r="K30" t="n">
-        <v>362.54</v>
+        <v>362.51</v>
       </c>
       <c r="L30" t="n">
-        <v>355.414</v>
+        <v>355.362</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4905</v>
+        <v>0.4883</v>
       </c>
       <c r="N30" t="n">
-        <v>4.604</v>
+        <v>4.6035</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1088</v>
+        <v>0.1087</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1088</v>
+        <v>0.1087</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0446</v>
+        <v>0.0445</v>
       </c>
       <c r="S30" t="n">
-        <v>4565</v>
+        <v>4567</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1697</v>
+        <v>3.1705</v>
       </c>
       <c r="U30" t="n">
-        <v>28.35</v>
+        <v>28.23</v>
       </c>
       <c r="V30" t="n">
-        <v>2.5516</v>
+        <v>2.5514</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2245</v>
+        <v>2.2243</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.665</v>
+        <v>31.666</v>
       </c>
       <c r="B31" t="n">
         <v>74.8319</v>
@@ -3224,34 +3224,34 @@
         <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.3471</v>
+        <v>-1.3505</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.3462</v>
+        <v>-1.3495</v>
       </c>
       <c r="G31" t="n">
-        <v>23.744409</v>
+        <v>23.739047</v>
       </c>
       <c r="H31" t="n">
-        <v>23.743533</v>
+        <v>23.738182</v>
       </c>
       <c r="I31" t="n">
-        <v>29.3145</v>
+        <v>29.3153</v>
       </c>
       <c r="J31" t="n">
-        <v>29.3125</v>
+        <v>29.3132</v>
       </c>
       <c r="K31" t="n">
-        <v>362.121</v>
+        <v>362.075</v>
       </c>
       <c r="L31" t="n">
-        <v>354.947</v>
+        <v>354.937</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4593</v>
+        <v>0.4547</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6055</v>
+        <v>4.6057</v>
       </c>
       <c r="O31" t="n">
         <v>0.1098</v>
@@ -3260,28 +3260,28 @@
         <v>0.1098</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0719</v>
+        <v>0.0717</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0434</v>
+        <v>0.0432</v>
       </c>
       <c r="S31" t="n">
-        <v>4608</v>
+        <v>4609</v>
       </c>
       <c r="T31" t="n">
-        <v>3.1991</v>
+        <v>3.2001</v>
       </c>
       <c r="U31" t="n">
-        <v>33.81</v>
+        <v>34.03</v>
       </c>
       <c r="V31" t="n">
-        <v>2.5429</v>
+        <v>2.5424</v>
       </c>
       <c r="W31" t="n">
-        <v>2.217</v>
+        <v>2.2168</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32.655</v>
+        <v>32.656</v>
       </c>
       <c r="B32" t="n">
         <v>74.8319</v>
@@ -3322,58 +3322,58 @@
         <v>-1.3547</v>
       </c>
       <c r="G32" t="n">
-        <v>23.752617</v>
+        <v>23.750905</v>
       </c>
       <c r="H32" t="n">
-        <v>23.751438</v>
+        <v>23.749692</v>
       </c>
       <c r="I32" t="n">
-        <v>29.3331</v>
+        <v>29.3342</v>
       </c>
       <c r="J32" t="n">
-        <v>29.3309</v>
+        <v>29.3321</v>
       </c>
       <c r="K32" t="n">
-        <v>360.685</v>
+        <v>360.61</v>
       </c>
       <c r="L32" t="n">
-        <v>353.351</v>
+        <v>353.313</v>
       </c>
       <c r="M32" t="n">
-        <v>0.509</v>
+        <v>0.5246</v>
       </c>
       <c r="N32" t="n">
-        <v>4.606</v>
+        <v>4.6058</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1099</v>
+        <v>0.11</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1099</v>
+        <v>0.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0714</v>
+        <v>0.0716</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0454</v>
+        <v>0.046</v>
       </c>
       <c r="S32" t="n">
-        <v>4660</v>
+        <v>4662</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2354</v>
+        <v>3.2371</v>
       </c>
       <c r="U32" t="n">
-        <v>36.46</v>
+        <v>36.33</v>
       </c>
       <c r="V32" t="n">
-        <v>2.5343</v>
+        <v>2.5338</v>
       </c>
       <c r="W32" t="n">
-        <v>2.209</v>
+        <v>2.2088</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33.644</v>
+        <v>33.642</v>
       </c>
       <c r="B33" t="n">
         <v>74.8319</v>
@@ -3408,64 +3408,64 @@
         <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2856</v>
+        <v>-1.2851</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2855</v>
+        <v>-1.2849</v>
       </c>
       <c r="G33" t="n">
-        <v>23.832116</v>
+        <v>23.83328</v>
       </c>
       <c r="H33" t="n">
-        <v>23.830252</v>
+        <v>23.831473</v>
       </c>
       <c r="I33" t="n">
-        <v>29.3716</v>
+        <v>29.3728</v>
       </c>
       <c r="J33" t="n">
-        <v>29.3689</v>
+        <v>29.3702</v>
       </c>
       <c r="K33" t="n">
-        <v>359.172</v>
+        <v>359.116</v>
       </c>
       <c r="L33" t="n">
-        <v>351.507</v>
+        <v>351.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5493</v>
+        <v>0.5698</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6061</v>
+        <v>4.6064</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1097</v>
+        <v>0.1098</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1097</v>
+        <v>0.1098</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0714</v>
+        <v>0.0711</v>
       </c>
       <c r="R33" t="n">
-        <v>0.047</v>
+        <v>0.0478</v>
       </c>
       <c r="S33" t="n">
-        <v>4719</v>
+        <v>4722</v>
       </c>
       <c r="T33" t="n">
-        <v>3.2762</v>
+        <v>3.2781</v>
       </c>
       <c r="U33" t="n">
-        <v>29.9</v>
+        <v>30.52</v>
       </c>
       <c r="V33" t="n">
-        <v>2.5303</v>
+        <v>2.5301</v>
       </c>
       <c r="W33" t="n">
-        <v>2.204</v>
+        <v>2.2042</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3500,64 +3500,64 @@
         <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2886</v>
+        <v>-1.2895</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2884</v>
+        <v>-1.2893</v>
       </c>
       <c r="G34" t="n">
-        <v>23.856189</v>
+        <v>23.856168</v>
       </c>
       <c r="H34" t="n">
-        <v>23.854901</v>
+        <v>23.854844</v>
       </c>
       <c r="I34" t="n">
-        <v>29.4065</v>
+        <v>29.4077</v>
       </c>
       <c r="J34" t="n">
-        <v>29.4045</v>
+        <v>29.4058</v>
       </c>
       <c r="K34" t="n">
-        <v>359.367</v>
+        <v>359.362</v>
       </c>
       <c r="L34" t="n">
-        <v>350.927</v>
+        <v>350.882</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5372</v>
+        <v>0.5402</v>
       </c>
       <c r="N34" t="n">
-        <v>4.604</v>
+        <v>4.6046</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1085</v>
+        <v>0.1084</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1085</v>
+        <v>0.1084</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0732</v>
+        <v>0.0727</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0465</v>
+        <v>0.0466</v>
       </c>
       <c r="S34" t="n">
-        <v>4762</v>
+        <v>4763</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3064</v>
+        <v>3.3072</v>
       </c>
       <c r="U34" t="n">
-        <v>32.38</v>
+        <v>31.92</v>
       </c>
       <c r="V34" t="n">
-        <v>2.5316</v>
+        <v>2.5315</v>
       </c>
       <c r="W34" t="n">
-        <v>2.2013</v>
+        <v>2.2011</v>
       </c>
       <c r="X34" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35.623</v>
+        <v>35.626</v>
       </c>
       <c r="B35" t="n">
         <v>74.8319</v>
@@ -3592,64 +3592,64 @@
         <v>36</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3245</v>
+        <v>-1.3267</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.324</v>
+        <v>-1.3264</v>
       </c>
       <c r="G35" t="n">
-        <v>23.859147</v>
+        <v>23.858002</v>
       </c>
       <c r="H35" t="n">
-        <v>23.857849</v>
+        <v>23.8567</v>
       </c>
       <c r="I35" t="n">
+        <v>29.4473</v>
+      </c>
+      <c r="J35" t="n">
         <v>29.4453</v>
       </c>
-      <c r="J35" t="n">
-        <v>29.4431</v>
-      </c>
       <c r="K35" t="n">
-        <v>360.741</v>
+        <v>360.821</v>
       </c>
       <c r="L35" t="n">
-        <v>351.377</v>
+        <v>351.461</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6427</v>
+        <v>0.6488</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6082</v>
+        <v>4.6084</v>
       </c>
       <c r="O35" t="n">
-        <v>0.11</v>
+        <v>0.1102</v>
       </c>
       <c r="P35" t="n">
-        <v>0.11</v>
+        <v>0.1102</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0696</v>
+        <v>0.0694</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0507</v>
+        <v>0.051</v>
       </c>
       <c r="S35" t="n">
-        <v>4807</v>
+        <v>4811</v>
       </c>
       <c r="T35" t="n">
-        <v>3.3375</v>
+        <v>3.3402</v>
       </c>
       <c r="U35" t="n">
-        <v>21.35</v>
+        <v>23.98</v>
       </c>
       <c r="V35" t="n">
-        <v>2.5375</v>
+        <v>2.5378</v>
       </c>
       <c r="W35" t="n">
-        <v>2.2019</v>
+        <v>2.2023</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36.613</v>
+        <v>36.609</v>
       </c>
       <c r="B36" t="n">
-        <v>74.83192</v>
+        <v>74.83191</v>
       </c>
       <c r="C36" t="n">
         <v>170.807</v>
@@ -3684,64 +3684,64 @@
         <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3681</v>
+        <v>-1.3692</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3682</v>
+        <v>-1.3703</v>
       </c>
       <c r="G36" t="n">
-        <v>23.840686</v>
+        <v>23.840368</v>
       </c>
       <c r="H36" t="n">
-        <v>23.856509</v>
+        <v>23.854669</v>
       </c>
       <c r="I36" t="n">
-        <v>29.4628</v>
+        <v>29.4656</v>
       </c>
       <c r="J36" t="n">
-        <v>29.4843</v>
+        <v>29.4862</v>
       </c>
       <c r="K36" t="n">
-        <v>361.558</v>
+        <v>361.653</v>
       </c>
       <c r="L36" t="n">
-        <v>350.215</v>
+        <v>350.324</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7122</v>
+        <v>0.7109</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6104</v>
+        <v>4.6107</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1105</v>
+        <v>0.1106</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1105</v>
+        <v>0.1106</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0676</v>
+        <v>0.0674</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0535</v>
+        <v>0.0534</v>
       </c>
       <c r="S36" t="n">
-        <v>4875</v>
+        <v>4879</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3849</v>
+        <v>3.3874</v>
       </c>
       <c r="U36" t="n">
-        <v>32.29</v>
+        <v>33.16</v>
       </c>
       <c r="V36" t="n">
-        <v>2.5394</v>
+        <v>2.5399</v>
       </c>
       <c r="W36" t="n">
-        <v>2.1944</v>
+        <v>2.1949</v>
       </c>
       <c r="X36" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3776,64 +3776,64 @@
         <v>38</v>
       </c>
       <c r="E37" t="n">
+        <v>-1.4054</v>
+      </c>
+      <c r="F37" t="n">
         <v>-1.4049</v>
       </c>
-      <c r="F37" t="n">
-        <v>-1.4045</v>
-      </c>
       <c r="G37" t="n">
-        <v>23.890978</v>
+        <v>23.889553</v>
       </c>
       <c r="H37" t="n">
-        <v>23.889389</v>
+        <v>23.887329</v>
       </c>
       <c r="I37" t="n">
-        <v>29.5668</v>
+        <v>29.5682</v>
       </c>
       <c r="J37" t="n">
-        <v>29.5642</v>
+        <v>29.5646</v>
       </c>
       <c r="K37" t="n">
-        <v>360.547</v>
+        <v>360.515</v>
       </c>
       <c r="L37" t="n">
-        <v>352.332</v>
+        <v>352.39</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6201</v>
+        <v>0.6164</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6063</v>
+        <v>4.6062</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1107</v>
+        <v>0.1106</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1107</v>
+        <v>0.1106</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0712</v>
+        <v>0.0713</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0498</v>
+        <v>0.0497</v>
       </c>
       <c r="S37" t="n">
-        <v>4920</v>
+        <v>4921</v>
       </c>
       <c r="T37" t="n">
-        <v>3.4162</v>
+        <v>3.4169</v>
       </c>
       <c r="U37" t="n">
-        <v>31.39</v>
+        <v>31.37</v>
       </c>
       <c r="V37" t="n">
-        <v>2.5328</v>
+        <v>2.5326</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2035</v>
+        <v>2.2038</v>
       </c>
       <c r="X37" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38.591</v>
+        <v>38.594</v>
       </c>
       <c r="B38" t="n">
         <v>74.83192</v>
@@ -3868,64 +3868,64 @@
         <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4307</v>
+        <v>-1.4274</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4301</v>
+        <v>-1.4269</v>
       </c>
       <c r="G38" t="n">
-        <v>24.071426</v>
+        <v>24.08351</v>
       </c>
       <c r="H38" t="n">
-        <v>24.074134</v>
+        <v>24.085782</v>
       </c>
       <c r="I38" t="n">
-        <v>29.8369</v>
+        <v>29.853</v>
       </c>
       <c r="J38" t="n">
-        <v>29.84</v>
+        <v>29.8556</v>
       </c>
       <c r="K38" t="n">
-        <v>357.673</v>
+        <v>357.2</v>
       </c>
       <c r="L38" t="n">
-        <v>350.779</v>
+        <v>350.473</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4289</v>
+        <v>0.4324</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6021</v>
+        <v>4.6023</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1121</v>
+        <v>0.1122</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1121</v>
+        <v>0.1122</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0749</v>
+        <v>0.0747</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0421</v>
+        <v>0.0423</v>
       </c>
       <c r="S38" t="n">
-        <v>4958</v>
+        <v>4960</v>
       </c>
       <c r="T38" t="n">
-        <v>3.4422</v>
+        <v>3.4439</v>
       </c>
       <c r="U38" t="n">
-        <v>30.37</v>
+        <v>30.32</v>
       </c>
       <c r="V38" t="n">
-        <v>2.519</v>
+        <v>2.5167</v>
       </c>
       <c r="W38" t="n">
-        <v>2.1982</v>
+        <v>2.1971</v>
       </c>
       <c r="X38" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39.581</v>
+        <v>39.58</v>
       </c>
       <c r="B39" t="n">
         <v>74.83192</v>
@@ -3960,64 +3960,64 @@
         <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4124</v>
+        <v>-1.4119</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4117</v>
+        <v>-1.4112</v>
       </c>
       <c r="G39" t="n">
-        <v>24.24395</v>
+        <v>24.246589</v>
       </c>
       <c r="H39" t="n">
-        <v>24.248189</v>
+        <v>24.25209</v>
       </c>
       <c r="I39" t="n">
-        <v>30.0525</v>
+        <v>30.0571</v>
       </c>
       <c r="J39" t="n">
-        <v>30.0575</v>
+        <v>30.0638</v>
       </c>
       <c r="K39" t="n">
-        <v>345.15</v>
+        <v>344.786</v>
       </c>
       <c r="L39" t="n">
-        <v>341.446</v>
+        <v>341.161</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4298</v>
+        <v>0.4283</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6059</v>
+        <v>4.606</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1166</v>
+        <v>0.1169</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1166</v>
+        <v>0.1169</v>
       </c>
       <c r="Q39" t="n">
         <v>0.0715</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0422</v>
+        <v>0.0421</v>
       </c>
       <c r="S39" t="n">
-        <v>5021</v>
+        <v>5023</v>
       </c>
       <c r="T39" t="n">
-        <v>3.4863</v>
+        <v>3.4878</v>
       </c>
       <c r="U39" t="n">
-        <v>29.27</v>
+        <v>29.23</v>
       </c>
       <c r="V39" t="n">
-        <v>2.4522</v>
+        <v>2.4502</v>
       </c>
       <c r="W39" t="n">
-        <v>2.157</v>
+        <v>2.1558</v>
       </c>
       <c r="X39" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40.57</v>
+        <v>40.568</v>
       </c>
       <c r="B40" t="n">
         <v>74.83192</v>
@@ -4052,64 +4052,64 @@
         <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3995</v>
+        <v>-1.3989</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3988</v>
+        <v>-1.3982</v>
       </c>
       <c r="G40" t="n">
-        <v>24.442649</v>
+        <v>24.459765</v>
       </c>
       <c r="H40" t="n">
-        <v>24.443472</v>
+        <v>24.460674</v>
       </c>
       <c r="I40" t="n">
-        <v>30.3091</v>
+        <v>30.3324</v>
       </c>
       <c r="J40" t="n">
-        <v>30.3095</v>
+        <v>30.3329</v>
       </c>
       <c r="K40" t="n">
-        <v>326.017</v>
+        <v>325.457</v>
       </c>
       <c r="L40" t="n">
-        <v>326.115</v>
+        <v>325.604</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4886</v>
+        <v>0.4858</v>
       </c>
       <c r="N40" t="n">
         <v>4.61</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1174</v>
+        <v>0.1175</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1174</v>
+        <v>0.1175</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0679</v>
+        <v>0.068</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0446</v>
+        <v>0.0445</v>
       </c>
       <c r="S40" t="n">
-        <v>5077</v>
+        <v>5079</v>
       </c>
       <c r="T40" t="n">
-        <v>3.5252</v>
+        <v>3.5262</v>
       </c>
       <c r="U40" t="n">
-        <v>28.27</v>
+        <v>28.25</v>
       </c>
       <c r="V40" t="n">
-        <v>2.3477</v>
+        <v>2.3449</v>
       </c>
       <c r="W40" t="n">
-        <v>2.087</v>
+        <v>2.0848</v>
       </c>
       <c r="X40" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41.56</v>
+        <v>41.561</v>
       </c>
       <c r="B41" t="n">
         <v>74.83192</v>
@@ -4144,64 +4144,64 @@
         <v>42</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3871</v>
+        <v>-1.3868</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3863</v>
+        <v>-1.386</v>
       </c>
       <c r="G41" t="n">
-        <v>24.829982</v>
+        <v>24.839299</v>
       </c>
       <c r="H41" t="n">
-        <v>24.833181</v>
+        <v>24.842245</v>
       </c>
       <c r="I41" t="n">
-        <v>30.823</v>
+        <v>30.8356</v>
       </c>
       <c r="J41" t="n">
-        <v>30.8265</v>
+        <v>30.8388</v>
       </c>
       <c r="K41" t="n">
-        <v>311.657</v>
+        <v>311.276</v>
       </c>
       <c r="L41" t="n">
-        <v>312.223</v>
+        <v>311.913</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4194</v>
+        <v>0.4215</v>
       </c>
       <c r="N41" t="n">
-        <v>4.6128</v>
+        <v>4.6129</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0655</v>
+        <v>0.0654</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0418</v>
+        <v>0.0419</v>
       </c>
       <c r="S41" t="n">
-        <v>5118</v>
+        <v>5119</v>
       </c>
       <c r="T41" t="n">
-        <v>3.5534</v>
+        <v>3.5542</v>
       </c>
       <c r="U41" t="n">
-        <v>27.26</v>
+        <v>27.21</v>
       </c>
       <c r="V41" t="n">
-        <v>2.2737</v>
+        <v>2.2717</v>
       </c>
       <c r="W41" t="n">
-        <v>2.0267</v>
+        <v>2.0254</v>
       </c>
       <c r="X41" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -4224,13 +4224,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42.549</v>
+        <v>42.551</v>
       </c>
       <c r="B42" t="n">
-        <v>74.83193</v>
+        <v>74.83194</v>
       </c>
       <c r="C42" t="n">
-        <v>170.80703</v>
+        <v>170.80704</v>
       </c>
       <c r="D42" t="n">
         <v>43</v>
@@ -4239,61 +4239,61 @@
         <v>-1.3803</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.3797</v>
+        <v>-1.3796</v>
       </c>
       <c r="G42" t="n">
-        <v>25.044311</v>
+        <v>25.049589</v>
       </c>
       <c r="H42" t="n">
-        <v>25.050998</v>
+        <v>25.057001</v>
       </c>
       <c r="I42" t="n">
-        <v>31.1076</v>
+        <v>31.1147</v>
       </c>
       <c r="J42" t="n">
-        <v>31.1161</v>
+        <v>31.1241</v>
       </c>
       <c r="K42" t="n">
-        <v>292.981</v>
+        <v>291.882</v>
       </c>
       <c r="L42" t="n">
-        <v>264.362</v>
+        <v>262.857</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3918</v>
+        <v>0.3897</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6122</v>
+        <v>4.6124</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1285</v>
+        <v>0.1288</v>
       </c>
       <c r="P42" t="n">
-        <v>0.1285</v>
+        <v>0.1288</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0661</v>
+        <v>0.0658</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0407</v>
+        <v>0.0406</v>
       </c>
       <c r="S42" t="n">
-        <v>5166</v>
+        <v>5169</v>
       </c>
       <c r="T42" t="n">
-        <v>3.5871</v>
+        <v>3.5885</v>
       </c>
       <c r="U42" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="V42" t="n">
-        <v>2.1708</v>
+        <v>2.1646</v>
       </c>
       <c r="W42" t="n">
-        <v>1.7985</v>
+        <v>1.7913</v>
       </c>
       <c r="X42" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43.539</v>
+        <v>43.536</v>
       </c>
       <c r="B43" t="n">
         <v>74.83194</v>
@@ -4328,64 +4328,64 @@
         <v>44</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.3767</v>
+        <v>-1.3765</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.3762</v>
+        <v>-1.376</v>
       </c>
       <c r="G43" t="n">
-        <v>25.276447</v>
+        <v>25.286513</v>
       </c>
       <c r="H43" t="n">
-        <v>25.28158</v>
+        <v>25.291681</v>
       </c>
       <c r="I43" t="n">
-        <v>31.42</v>
+        <v>31.4333</v>
       </c>
       <c r="J43" t="n">
-        <v>31.4264</v>
+        <v>31.4398</v>
       </c>
       <c r="K43" t="n">
-        <v>265.547</v>
+        <v>264.068</v>
       </c>
       <c r="L43" t="n">
-        <v>264.702</v>
+        <v>265.672</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3873</v>
+        <v>0.3837</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6136</v>
+        <v>4.6134</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1349</v>
+        <v>0.1353</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1349</v>
+        <v>0.1353</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0648</v>
+        <v>0.065</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0405</v>
+        <v>0.0404</v>
       </c>
       <c r="S43" t="n">
-        <v>5231</v>
+        <v>5234</v>
       </c>
       <c r="T43" t="n">
-        <v>3.6321</v>
+        <v>3.6342</v>
       </c>
       <c r="U43" t="n">
-        <v>25.14</v>
+        <v>25.09</v>
       </c>
       <c r="V43" t="n">
-        <v>2.0174</v>
+        <v>2.0091</v>
       </c>
       <c r="W43" t="n">
-        <v>1.8033</v>
+        <v>1.8082</v>
       </c>
       <c r="X43" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -4426,58 +4426,58 @@
         <v>-1.3745</v>
       </c>
       <c r="G44" t="n">
-        <v>25.494815</v>
+        <v>25.499134</v>
       </c>
       <c r="H44" t="n">
-        <v>25.492414</v>
+        <v>25.496908</v>
       </c>
       <c r="I44" t="n">
-        <v>31.7158</v>
+        <v>31.7215</v>
       </c>
       <c r="J44" t="n">
-        <v>31.712</v>
+        <v>31.718</v>
       </c>
       <c r="K44" t="n">
-        <v>251.976</v>
+        <v>251.956</v>
       </c>
       <c r="L44" t="n">
-        <v>255.097</v>
+        <v>254.88</v>
       </c>
       <c r="M44" t="n">
         <v>0.3544</v>
       </c>
       <c r="N44" t="n">
-        <v>4.6095</v>
+        <v>4.609</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1379</v>
+        <v>0.138</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1379</v>
+        <v>0.138</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0684</v>
+        <v>0.0688</v>
       </c>
       <c r="R44" t="n">
         <v>0.0392</v>
       </c>
       <c r="S44" t="n">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="T44" t="n">
-        <v>3.6633</v>
+        <v>3.6638</v>
       </c>
       <c r="U44" t="n">
-        <v>24.13</v>
+        <v>24.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.9428</v>
+        <v>1.9427</v>
       </c>
       <c r="W44" t="n">
-        <v>1.7594</v>
+        <v>1.7584</v>
       </c>
       <c r="X44" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45.517</v>
+        <v>45.521</v>
       </c>
       <c r="B45" t="n">
         <v>74.83194</v>
@@ -4512,64 +4512,64 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.3695</v>
+        <v>-1.3693</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.3692</v>
+        <v>-1.3689</v>
       </c>
       <c r="G45" t="n">
-        <v>25.68525</v>
+        <v>25.686758</v>
       </c>
       <c r="H45" t="n">
-        <v>25.687657</v>
+        <v>25.690289</v>
       </c>
       <c r="I45" t="n">
-        <v>31.9698</v>
+        <v>31.9713</v>
       </c>
       <c r="J45" t="n">
-        <v>31.9727</v>
+        <v>31.9758</v>
       </c>
       <c r="K45" t="n">
-        <v>244.486</v>
+        <v>244.073</v>
       </c>
       <c r="L45" t="n">
-        <v>245.914</v>
+        <v>245.37</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3613</v>
+        <v>0.3594</v>
       </c>
       <c r="N45" t="n">
-        <v>4.6087</v>
+        <v>4.6094</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1354</v>
+        <v>0.1351</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1354</v>
+        <v>0.1351</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0691</v>
+        <v>0.0685</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0395</v>
+        <v>0.0394</v>
       </c>
       <c r="S45" t="n">
-        <v>5318</v>
+        <v>5320</v>
       </c>
       <c r="T45" t="n">
-        <v>3.6922</v>
+        <v>3.6941</v>
       </c>
       <c r="U45" t="n">
-        <v>22.84</v>
+        <v>22.87</v>
       </c>
       <c r="V45" t="n">
-        <v>1.9025</v>
+        <v>1.9002</v>
       </c>
       <c r="W45" t="n">
-        <v>1.7172</v>
+        <v>1.7146</v>
       </c>
       <c r="X45" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46.507</v>
+        <v>46.503</v>
       </c>
       <c r="B46" t="n">
         <v>74.83194</v>
@@ -4604,64 +4604,64 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.3685</v>
+        <v>-1.3687</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.3682</v>
+        <v>-1.3684</v>
       </c>
       <c r="G46" t="n">
-        <v>25.851051</v>
+        <v>25.853917</v>
       </c>
       <c r="H46" t="n">
-        <v>25.859872</v>
+        <v>25.864991</v>
       </c>
       <c r="I46" t="n">
-        <v>32.195</v>
+        <v>32.1988</v>
       </c>
       <c r="J46" t="n">
-        <v>32.2067</v>
+        <v>32.2137</v>
       </c>
       <c r="K46" t="n">
-        <v>226.702</v>
+        <v>226.47</v>
       </c>
       <c r="L46" t="n">
-        <v>210.258</v>
+        <v>209.944</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3678</v>
+        <v>0.3611</v>
       </c>
       <c r="N46" t="n">
-        <v>4.6128</v>
+        <v>4.6134</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1316</v>
+        <v>0.1311</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1316</v>
+        <v>0.1311</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0655</v>
+        <v>0.065</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0397</v>
+        <v>0.0395</v>
       </c>
       <c r="S46" t="n">
-        <v>5385</v>
+        <v>5388</v>
       </c>
       <c r="T46" t="n">
-        <v>3.7389</v>
+        <v>3.7413</v>
       </c>
       <c r="U46" t="n">
-        <v>22.02</v>
+        <v>21.98</v>
       </c>
       <c r="V46" t="n">
-        <v>1.8021</v>
+        <v>1.8008</v>
       </c>
       <c r="W46" t="n">
-        <v>1.5452</v>
+        <v>1.5437</v>
       </c>
       <c r="X46" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47.496</v>
+        <v>47.497</v>
       </c>
       <c r="B47" t="n">
         <v>74.83194</v>
@@ -4696,64 +4696,64 @@
         <v>48</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.3475</v>
+        <v>-1.3473</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.3469</v>
+        <v>-1.3466</v>
       </c>
       <c r="G47" t="n">
-        <v>26.076825</v>
+        <v>26.081082</v>
       </c>
       <c r="H47" t="n">
-        <v>26.075555</v>
+        <v>26.080328</v>
       </c>
       <c r="I47" t="n">
-        <v>32.4808</v>
+        <v>32.4856</v>
       </c>
       <c r="J47" t="n">
-        <v>32.4784</v>
+        <v>32.4838</v>
       </c>
       <c r="K47" t="n">
-        <v>203.205</v>
+        <v>202.885</v>
       </c>
       <c r="L47" t="n">
-        <v>199.903</v>
+        <v>199.474</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3051</v>
+        <v>0.3002</v>
       </c>
       <c r="N47" t="n">
-        <v>4.6034</v>
+        <v>4.603</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1312</v>
+        <v>0.1311</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1312</v>
+        <v>0.1311</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0372</v>
+        <v>0.037</v>
       </c>
       <c r="S47" t="n">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="T47" t="n">
-        <v>3.7705</v>
+        <v>3.7712</v>
       </c>
       <c r="U47" t="n">
-        <v>21.09</v>
+        <v>21.04</v>
       </c>
       <c r="V47" t="n">
-        <v>1.6696</v>
+        <v>1.6678</v>
       </c>
       <c r="W47" t="n">
-        <v>1.4973</v>
+        <v>1.4952</v>
       </c>
       <c r="X47" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48.486</v>
+        <v>48.488</v>
       </c>
       <c r="B48" t="n">
         <v>74.83195</v>
@@ -4794,28 +4794,28 @@
         <v>-1.343</v>
       </c>
       <c r="G48" t="n">
-        <v>26.203452</v>
+        <v>26.207842</v>
       </c>
       <c r="H48" t="n">
-        <v>26.204821</v>
+        <v>26.209111</v>
       </c>
       <c r="I48" t="n">
-        <v>32.6493</v>
+        <v>32.6545</v>
       </c>
       <c r="J48" t="n">
-        <v>32.6507</v>
+        <v>32.6557</v>
       </c>
       <c r="K48" t="n">
-        <v>187.209</v>
+        <v>186.489</v>
       </c>
       <c r="L48" t="n">
-        <v>193.892</v>
+        <v>193.288</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2215</v>
+        <v>0.2222</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5976</v>
+        <v>4.5978</v>
       </c>
       <c r="O48" t="n">
         <v>0.1323</v>
@@ -4824,28 +4824,28 @@
         <v>0.1323</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.0787</v>
+        <v>0.0786</v>
       </c>
       <c r="R48" t="n">
         <v>0.0339</v>
       </c>
       <c r="S48" t="n">
-        <v>5473</v>
+        <v>5475</v>
       </c>
       <c r="T48" t="n">
-        <v>3.8</v>
+        <v>3.8012</v>
       </c>
       <c r="U48" t="n">
-        <v>20</v>
+        <v>19.97</v>
       </c>
       <c r="V48" t="n">
-        <v>1.5784</v>
+        <v>1.5743</v>
       </c>
       <c r="W48" t="n">
-        <v>1.4691</v>
+        <v>1.4662</v>
       </c>
       <c r="X48" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49.475</v>
+        <v>49.474</v>
       </c>
       <c r="B49" t="n">
         <v>74.83196</v>
@@ -4880,64 +4880,64 @@
         <v>50</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.3426</v>
+        <v>-1.3434</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.3422</v>
+        <v>-1.343</v>
       </c>
       <c r="G49" t="n">
-        <v>26.29495</v>
+        <v>26.298611</v>
       </c>
       <c r="H49" t="n">
-        <v>26.298994</v>
+        <v>26.302559</v>
       </c>
       <c r="I49" t="n">
-        <v>32.7731</v>
+        <v>32.7785</v>
       </c>
       <c r="J49" t="n">
-        <v>32.7783</v>
+        <v>32.7834</v>
       </c>
       <c r="K49" t="n">
-        <v>160.879</v>
+        <v>160.459</v>
       </c>
       <c r="L49" t="n">
-        <v>169.286</v>
+        <v>168.684</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2556</v>
+        <v>0.2534</v>
       </c>
       <c r="N49" t="n">
-        <v>4.6097</v>
+        <v>4.6098</v>
       </c>
       <c r="O49" t="n">
-        <v>0.1315</v>
+        <v>0.1314</v>
       </c>
       <c r="P49" t="n">
-        <v>0.1315</v>
+        <v>0.1314</v>
       </c>
       <c r="Q49" t="n">
         <v>0.0682</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0352</v>
+        <v>0.0351</v>
       </c>
       <c r="S49" t="n">
-        <v>5536</v>
+        <v>5538</v>
       </c>
       <c r="T49" t="n">
-        <v>3.8437</v>
+        <v>3.8452</v>
       </c>
       <c r="U49" t="n">
-        <v>18.94</v>
+        <v>18.91</v>
       </c>
       <c r="V49" t="n">
-        <v>1.4265</v>
+        <v>1.4241</v>
       </c>
       <c r="W49" t="n">
-        <v>1.3493</v>
+        <v>1.3463</v>
       </c>
       <c r="X49" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -4972,34 +4972,34 @@
         <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.3725</v>
+        <v>-1.3745</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.3722</v>
+        <v>-1.3742</v>
       </c>
       <c r="G50" t="n">
-        <v>26.378479</v>
+        <v>26.380522</v>
       </c>
       <c r="H50" t="n">
-        <v>26.377344</v>
+        <v>26.37941</v>
       </c>
       <c r="I50" t="n">
-        <v>32.9201</v>
+        <v>32.9257</v>
       </c>
       <c r="J50" t="n">
-        <v>32.9182</v>
+        <v>32.9238</v>
       </c>
       <c r="K50" t="n">
-        <v>151.595</v>
+        <v>151.415</v>
       </c>
       <c r="L50" t="n">
-        <v>157.114</v>
+        <v>156.856</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2441</v>
+        <v>0.2438</v>
       </c>
       <c r="N50" t="n">
-        <v>4.6126</v>
+        <v>4.6125</v>
       </c>
       <c r="O50" t="n">
         <v>0.133</v>
@@ -5008,28 +5008,28 @@
         <v>0.133</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0657</v>
+        <v>0.0658</v>
       </c>
       <c r="R50" t="n">
         <v>0.0348</v>
       </c>
       <c r="S50" t="n">
-        <v>5586</v>
+        <v>5587</v>
       </c>
       <c r="T50" t="n">
-        <v>3.8784</v>
+        <v>3.8795</v>
       </c>
       <c r="U50" t="n">
-        <v>17.96</v>
+        <v>17.92</v>
       </c>
       <c r="V50" t="n">
-        <v>1.3727</v>
+        <v>1.3717</v>
       </c>
       <c r="W50" t="n">
-        <v>1.2896</v>
+        <v>1.2883</v>
       </c>
       <c r="X50" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51.454</v>
+        <v>51.455</v>
       </c>
       <c r="B51" t="n">
         <v>74.83196</v>
@@ -5064,64 +5064,64 @@
         <v>52</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.4033</v>
+        <v>-1.4019</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.402</v>
+        <v>-1.4007</v>
       </c>
       <c r="G51" t="n">
-        <v>26.453259</v>
+        <v>26.456728</v>
       </c>
       <c r="H51" t="n">
-        <v>26.454093</v>
+        <v>26.457705</v>
       </c>
       <c r="I51" t="n">
-        <v>33.0562</v>
+        <v>33.0608</v>
       </c>
       <c r="J51" t="n">
-        <v>33.0559</v>
+        <v>33.0607</v>
       </c>
       <c r="K51" t="n">
-        <v>154.08</v>
+        <v>155.188</v>
       </c>
       <c r="L51" t="n">
-        <v>153.477</v>
+        <v>153.993</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2043</v>
+        <v>0.1987</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6126</v>
+        <v>4.6127</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1329</v>
+        <v>0.1328</v>
       </c>
       <c r="P51" t="n">
-        <v>0.1329</v>
+        <v>0.1328</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0657</v>
+        <v>0.0656</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0332</v>
+        <v>0.033</v>
       </c>
       <c r="S51" t="n">
-        <v>5632</v>
+        <v>5634</v>
       </c>
       <c r="T51" t="n">
-        <v>3.9105</v>
+        <v>3.912</v>
       </c>
       <c r="U51" t="n">
-        <v>16.91</v>
+        <v>16.88</v>
       </c>
       <c r="V51" t="n">
-        <v>1.3872</v>
+        <v>1.3937</v>
       </c>
       <c r="W51" t="n">
-        <v>1.2718</v>
+        <v>1.2744</v>
       </c>
       <c r="X51" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -5156,64 +5156,64 @@
         <v>53</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.3734</v>
+        <v>-1.373</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.3732</v>
+        <v>-1.3729</v>
       </c>
       <c r="G52" t="n">
-        <v>26.578648</v>
+        <v>26.581942</v>
       </c>
       <c r="H52" t="n">
-        <v>26.579564</v>
+        <v>26.582753</v>
       </c>
       <c r="I52" t="n">
-        <v>33.1947</v>
+        <v>33.1989</v>
       </c>
       <c r="J52" t="n">
-        <v>33.1958</v>
+        <v>33.1999</v>
       </c>
       <c r="K52" t="n">
-        <v>184.998</v>
+        <v>186.015</v>
       </c>
       <c r="L52" t="n">
-        <v>173.186</v>
+        <v>174.154</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1536</v>
+        <v>0.1531</v>
       </c>
       <c r="N52" t="n">
-        <v>4.6102</v>
+        <v>4.6098</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1315</v>
+        <v>0.1312</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1315</v>
+        <v>0.1312</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0678</v>
+        <v>0.0681</v>
       </c>
       <c r="R52" t="n">
         <v>0.0311</v>
       </c>
       <c r="S52" t="n">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="T52" t="n">
-        <v>3.9469</v>
+        <v>3.9479</v>
       </c>
       <c r="U52" t="n">
-        <v>15.86</v>
+        <v>15.84</v>
       </c>
       <c r="V52" t="n">
-        <v>1.5687</v>
+        <v>1.5747</v>
       </c>
       <c r="W52" t="n">
-        <v>1.3701</v>
+        <v>1.3749</v>
       </c>
       <c r="X52" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -5248,64 +5248,64 @@
         <v>54</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.3679</v>
+        <v>-1.3663</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.3659</v>
+        <v>-1.3645</v>
       </c>
       <c r="G53" t="n">
-        <v>26.710954</v>
+        <v>26.7179</v>
       </c>
       <c r="H53" t="n">
-        <v>26.718452</v>
+        <v>26.725682</v>
       </c>
       <c r="I53" t="n">
-        <v>33.3699</v>
+        <v>33.3775</v>
       </c>
       <c r="J53" t="n">
-        <v>33.378</v>
+        <v>33.386</v>
       </c>
       <c r="K53" t="n">
-        <v>212.624</v>
+        <v>213.117</v>
       </c>
       <c r="L53" t="n">
-        <v>200.056</v>
+        <v>200.63</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1439</v>
+        <v>0.1417</v>
       </c>
       <c r="N53" t="n">
-        <v>4.6085</v>
+        <v>4.6084</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1276</v>
+        <v>0.1275</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1276</v>
+        <v>0.1275</v>
       </c>
       <c r="Q53" t="n">
         <v>0.0694</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0307</v>
+        <v>0.0306</v>
       </c>
       <c r="S53" t="n">
-        <v>5736</v>
+        <v>5738</v>
       </c>
       <c r="T53" t="n">
-        <v>3.9829</v>
+        <v>3.9839</v>
       </c>
       <c r="U53" t="n">
-        <v>14.84</v>
+        <v>14.81</v>
       </c>
       <c r="V53" t="n">
-        <v>1.7312</v>
+        <v>1.7342</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5037</v>
+        <v>1.5066</v>
       </c>
       <c r="X53" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>54.422</v>
+        <v>54.421</v>
       </c>
       <c r="B54" t="n">
         <v>74.83196</v>
@@ -5340,64 +5340,64 @@
         <v>55</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2971</v>
+        <v>-1.2968</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.2965</v>
+        <v>-1.2964</v>
       </c>
       <c r="G54" t="n">
-        <v>26.990488</v>
+        <v>26.994527</v>
       </c>
       <c r="H54" t="n">
-        <v>26.995183</v>
+        <v>26.997643</v>
       </c>
       <c r="I54" t="n">
-        <v>33.674</v>
+        <v>33.677</v>
       </c>
       <c r="J54" t="n">
-        <v>33.6798</v>
+        <v>33.6808</v>
       </c>
       <c r="K54" t="n">
-        <v>223.735</v>
+        <v>223.917</v>
       </c>
       <c r="L54" t="n">
-        <v>214.425</v>
+        <v>214.584</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0353</v>
+        <v>0.0279</v>
       </c>
       <c r="N54" t="n">
-        <v>4.6066</v>
+        <v>4.6064</v>
       </c>
       <c r="O54" t="n">
-        <v>0.1241</v>
+        <v>0.1242</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1241</v>
+        <v>0.1242</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.071</v>
+        <v>0.0711</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0264</v>
+        <v>0.0261</v>
       </c>
       <c r="S54" t="n">
-        <v>5789</v>
+        <v>5791</v>
       </c>
       <c r="T54" t="n">
-        <v>4.0198</v>
+        <v>4.0209</v>
       </c>
       <c r="U54" t="n">
-        <v>13.82</v>
+        <v>13.78</v>
       </c>
       <c r="V54" t="n">
-        <v>1.8016</v>
+        <v>1.8027</v>
       </c>
       <c r="W54" t="n">
-        <v>1.579</v>
+        <v>1.5798</v>
       </c>
       <c r="X54" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="Y54" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55.411</v>
+        <v>55.412</v>
       </c>
       <c r="B55" t="n">
         <v>74.83198</v>
@@ -5432,64 +5432,64 @@
         <v>56</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.289</v>
+        <v>-1.2891</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2887</v>
+        <v>-1.2888</v>
       </c>
       <c r="G55" t="n">
-        <v>27.034842</v>
+        <v>27.036093</v>
       </c>
       <c r="H55" t="n">
-        <v>27.033072</v>
+        <v>27.034434</v>
       </c>
       <c r="I55" t="n">
-        <v>33.7252</v>
+        <v>33.7251</v>
       </c>
       <c r="J55" t="n">
-        <v>33.7225</v>
+        <v>33.7224</v>
       </c>
       <c r="K55" t="n">
-        <v>231.027</v>
+        <v>231.089</v>
       </c>
       <c r="L55" t="n">
-        <v>222.275</v>
+        <v>222.49</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0062</v>
+        <v>-0.0089</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6012</v>
+        <v>4.5999</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1245</v>
+        <v>0.1246</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1245</v>
+        <v>0.1246</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0756</v>
+        <v>0.0768</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0247</v>
+        <v>0.0246</v>
       </c>
       <c r="S55" t="n">
-        <v>5835</v>
+        <v>5837</v>
       </c>
       <c r="T55" t="n">
-        <v>4.0515</v>
+        <v>4.0526</v>
       </c>
       <c r="U55" t="n">
-        <v>12.79</v>
+        <v>12.75</v>
       </c>
       <c r="V55" t="n">
-        <v>1.845</v>
+        <v>1.8453</v>
       </c>
       <c r="W55" t="n">
-        <v>1.6183</v>
+        <v>1.6194</v>
       </c>
       <c r="X55" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56.4</v>
+        <v>56.401</v>
       </c>
       <c r="B56" t="n">
         <v>74.83198</v>
@@ -5530,58 +5530,58 @@
         <v>-1.2885</v>
       </c>
       <c r="G56" t="n">
-        <v>27.033931</v>
+        <v>27.035145</v>
       </c>
       <c r="H56" t="n">
-        <v>27.035575</v>
+        <v>27.036707</v>
       </c>
       <c r="I56" t="n">
-        <v>33.7234</v>
+        <v>33.7236</v>
       </c>
       <c r="J56" t="n">
-        <v>33.725</v>
+        <v>33.7251</v>
       </c>
       <c r="K56" t="n">
-        <v>231.735</v>
+        <v>231.743</v>
       </c>
       <c r="L56" t="n">
-        <v>225.382</v>
+        <v>225.553</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0049</v>
+        <v>-0.0057</v>
       </c>
       <c r="N56" t="n">
-        <v>4.5557</v>
+        <v>4.5539</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1248</v>
+        <v>0.125</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1248</v>
+        <v>0.125</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.1155</v>
+        <v>0.1171</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="S56" t="n">
-        <v>5885</v>
+        <v>5888</v>
       </c>
       <c r="T56" t="n">
-        <v>4.0864</v>
+        <v>4.088</v>
       </c>
       <c r="U56" t="n">
-        <v>11.73</v>
+        <v>11.69</v>
       </c>
       <c r="V56" t="n">
-        <v>1.8489</v>
+        <v>1.849</v>
       </c>
       <c r="W56" t="n">
-        <v>1.6335</v>
+        <v>1.6344</v>
       </c>
       <c r="X56" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>57.39</v>
+        <v>57.388</v>
       </c>
       <c r="B57" t="n">
         <v>74.83198</v>
@@ -5622,58 +5622,58 @@
         <v>-1.2883</v>
       </c>
       <c r="G57" t="n">
-        <v>27.037523</v>
+        <v>27.038467</v>
       </c>
       <c r="H57" t="n">
-        <v>27.036804</v>
+        <v>27.037652</v>
       </c>
       <c r="I57" t="n">
-        <v>33.7273</v>
+        <v>33.7275</v>
       </c>
       <c r="J57" t="n">
-        <v>33.7259</v>
+        <v>33.726</v>
       </c>
       <c r="K57" t="n">
-        <v>230.298</v>
+        <v>230.249</v>
       </c>
       <c r="L57" t="n">
-        <v>225.825</v>
+        <v>225.813</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.005</v>
+        <v>-0.0033</v>
       </c>
       <c r="N57" t="n">
-        <v>4.4018</v>
+        <v>4.4017</v>
       </c>
       <c r="O57" t="n">
-        <v>0.1252</v>
+        <v>0.1251</v>
       </c>
       <c r="P57" t="n">
-        <v>0.1252</v>
+        <v>0.1251</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.253</v>
+        <v>0.2532</v>
       </c>
       <c r="R57" t="n">
         <v>0.0248</v>
       </c>
       <c r="S57" t="n">
-        <v>5941</v>
+        <v>5944</v>
       </c>
       <c r="T57" t="n">
-        <v>4.125</v>
+        <v>4.1269</v>
       </c>
       <c r="U57" t="n">
-        <v>10.71</v>
+        <v>10.66</v>
       </c>
       <c r="V57" t="n">
-        <v>1.8404</v>
+        <v>1.8401</v>
       </c>
       <c r="W57" t="n">
-        <v>1.6356</v>
+        <v>1.6355</v>
       </c>
       <c r="X57" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -5714,58 +5714,58 @@
         <v>-1.2881</v>
       </c>
       <c r="G58" t="n">
-        <v>27.039657</v>
+        <v>27.040289</v>
       </c>
       <c r="H58" t="n">
-        <v>27.038121</v>
+        <v>27.03876</v>
       </c>
       <c r="I58" t="n">
-        <v>33.7293</v>
+        <v>33.7294</v>
       </c>
       <c r="J58" t="n">
-        <v>33.7268</v>
+        <v>33.7269</v>
       </c>
       <c r="K58" t="n">
-        <v>229.359</v>
+        <v>229.363</v>
       </c>
       <c r="L58" t="n">
-        <v>225.223</v>
+        <v>225.127</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="N58" t="n">
-        <v>4.341</v>
+        <v>4.3358</v>
       </c>
       <c r="O58" t="n">
-        <v>0.1244</v>
+        <v>0.1245</v>
       </c>
       <c r="P58" t="n">
-        <v>0.1244</v>
+        <v>0.1245</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.3088</v>
+        <v>0.3137</v>
       </c>
       <c r="R58" t="n">
-        <v>0.025</v>
+        <v>0.0251</v>
       </c>
       <c r="S58" t="n">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="T58" t="n">
-        <v>4.1575</v>
+        <v>4.1586</v>
       </c>
       <c r="U58" t="n">
-        <v>9.65</v>
+        <v>9.63</v>
       </c>
       <c r="V58" t="n">
         <v>1.8347</v>
       </c>
       <c r="W58" t="n">
-        <v>1.6325</v>
+        <v>1.632</v>
       </c>
       <c r="X58" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59.368</v>
+        <v>59.37</v>
       </c>
       <c r="B59" t="n">
         <v>74.83198</v>
@@ -5806,58 +5806,58 @@
         <v>-1.2881</v>
       </c>
       <c r="G59" t="n">
-        <v>27.039687</v>
+        <v>27.040018</v>
       </c>
       <c r="H59" t="n">
-        <v>27.03871</v>
+        <v>27.03919</v>
       </c>
       <c r="I59" t="n">
-        <v>33.7288</v>
+        <v>33.7286</v>
       </c>
       <c r="J59" t="n">
         <v>33.727</v>
       </c>
       <c r="K59" t="n">
-        <v>228.912</v>
+        <v>228.908</v>
       </c>
       <c r="L59" t="n">
-        <v>224.894</v>
+        <v>224.934</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0056</v>
+        <v>0.0034</v>
       </c>
       <c r="N59" t="n">
-        <v>4.2006</v>
+        <v>4.1917</v>
       </c>
       <c r="O59" t="n">
-        <v>0.1255</v>
+        <v>0.1256</v>
       </c>
       <c r="P59" t="n">
-        <v>0.1255</v>
+        <v>0.1256</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.4406</v>
+        <v>0.4491</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="S59" t="n">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="T59" t="n">
-        <v>4.1924</v>
+        <v>4.1946</v>
       </c>
       <c r="U59" t="n">
-        <v>8.63</v>
+        <v>8.58</v>
       </c>
       <c r="V59" t="n">
         <v>1.832</v>
       </c>
       <c r="W59" t="n">
-        <v>1.6307</v>
+        <v>1.6309</v>
       </c>
       <c r="X59" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -5880,46 +5880,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>60.358</v>
+        <v>60.361</v>
       </c>
       <c r="B60" t="n">
-        <v>74.83198</v>
+        <v>74.83199</v>
       </c>
       <c r="C60" t="n">
-        <v>170.80706</v>
+        <v>170.80704</v>
       </c>
       <c r="D60" t="n">
         <v>61</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.2893</v>
+        <v>-1.2895</v>
       </c>
       <c r="F60" t="n">
         <v>-1.2879</v>
       </c>
       <c r="G60" t="n">
-        <v>27.032554</v>
+        <v>27.032685</v>
       </c>
       <c r="H60" t="n">
-        <v>27.039005</v>
+        <v>27.039162</v>
       </c>
       <c r="I60" t="n">
-        <v>33.7193</v>
+        <v>33.7195</v>
       </c>
       <c r="J60" t="n">
         <v>33.7266</v>
       </c>
       <c r="K60" t="n">
-        <v>228.597</v>
+        <v>228.512</v>
       </c>
       <c r="L60" t="n">
-        <v>224.371</v>
+        <v>224.407</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0126</v>
+        <v>0.0094</v>
       </c>
       <c r="N60" t="n">
-        <v>4.0994</v>
+        <v>4.0946</v>
       </c>
       <c r="O60" t="n">
         <v>0.1251</v>
@@ -5928,28 +5928,28 @@
         <v>0.1251</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.538</v>
+        <v>0.5428</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0255</v>
+        <v>0.0253</v>
       </c>
       <c r="S60" t="n">
-        <v>6174</v>
+        <v>6358</v>
       </c>
       <c r="T60" t="n">
-        <v>4.287</v>
+        <v>4.4145</v>
       </c>
       <c r="U60" t="n">
-        <v>7.52</v>
+        <v>7.36</v>
       </c>
       <c r="V60" t="n">
-        <v>1.8298</v>
+        <v>1.8293</v>
       </c>
       <c r="W60" t="n">
-        <v>1.628</v>
+        <v>1.6282</v>
       </c>
       <c r="X60" t="n">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
@@ -5967,98 +5967,6 @@
         <v>32</v>
       </c>
       <c r="AD60" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>61.347</v>
-      </c>
-      <c r="B61" t="n">
-        <v>74.83205</v>
-      </c>
-      <c r="C61" t="n">
-        <v>170.80692</v>
-      </c>
-      <c r="D61" t="n">
-        <v>62</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-1.2875</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-1.2881</v>
-      </c>
-      <c r="G61" t="n">
-        <v>27.049015</v>
-      </c>
-      <c r="H61" t="n">
-        <v>27.0406</v>
-      </c>
-      <c r="I61" t="n">
-        <v>33.7392</v>
-      </c>
-      <c r="J61" t="n">
-        <v>33.7283</v>
-      </c>
-      <c r="K61" t="n">
-        <v>228.122</v>
-      </c>
-      <c r="L61" t="n">
-        <v>223.543</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="N61" t="n">
-        <v>4.0556</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0.1264</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.5807</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.0257</v>
-      </c>
-      <c r="S61" t="n">
-        <v>7887</v>
-      </c>
-      <c r="T61" t="n">
-        <v>5.4763</v>
-      </c>
-      <c r="U61" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.8271</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.6237</v>
-      </c>
-      <c r="X61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="1" t="n">
-        <v>45913.1004513889</v>
-      </c>
-      <c r="AA61" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB61" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC61" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD61" t="s">
         <v>33</v>
       </c>
     </row>
